--- a/affiliate_data/เครื่องใช้ในบ้าน.xlsx
+++ b/affiliate_data/เครื่องใช้ในบ้าน.xlsx
@@ -442,37 +442,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>TYESO รุ่นใหม่ 2026 แก้วเก็บความเย็นลายดอกไม้ 900ML แก้วเก็บอุณหภูมิสแตนเลส พร้อมหลอด เก็บเย็น 24H ร้อน 12H</v>
+        <v>เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ถึง160°c สีครีม เบาะฟองน้ำหนา10ซม. นุ่มสบาย ผ้ากำมะหยี่</v>
       </c>
       <c r="C2" t="str">
-        <v>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mlluqzaxv47981.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7rasb-m2j22x5ii5d008.webp</v>
       </c>
       <c r="D2" t="str">
-        <v>309.00</v>
+        <v>1699.00</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="G2" t="str">
-        <v>ขายได้ 455 ชิ้น</v>
+        <v>ขายได้ 49 ชิ้น</v>
       </c>
       <c r="H2" t="str">
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>https://shopee.co.th/product/0/54857018813</v>
+        <v>https://shopee.co.th/product/0/27467423728</v>
       </c>
       <c r="J2" t="str">
-        <v>https://s.shopee.co.th/9Uyt87gFze</v>
+        <v>https://s.shopee.co.th/2BCgYQIDQt</v>
       </c>
       <c r="K2" t="str">
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>12.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -480,37 +480,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Ozama บัลลังก์ รุ่น Alpha เก้าอี้เกมมิ่ง Gaming Chair by Tengu รับน้ำหนัก 150กก Throne of Gamer</v>
+        <v>Makita ไฟเบอร์ เครื่องตัดเหล็ก ขนาด 14 นิ้ว รุ่น 2414NB กำลังไฟ 3500 วัตต์ แถมฟรี ใบตัด 1 ใบ</v>
       </c>
       <c r="C3" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mozcimjqsxs236.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7r991-luwvpuv6v8t169.webp</v>
       </c>
       <c r="D3" t="str">
-        <v>6990.00</v>
+        <v>2660.00</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>38</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>ขายได้ 2พัน+ ชิ้น</v>
+        <v>ขายได้ 120 ชิ้น</v>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>https://shopee.co.th/product/0/24014645473</v>
+        <v>https://shopee.co.th/product/0/24928550424</v>
       </c>
       <c r="J3" t="str">
-        <v>https://s.shopee.co.th/110L0VMRke</v>
+        <v>https://s.shopee.co.th/40eKjnKRqk</v>
       </c>
       <c r="K3" t="str">
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -518,37 +518,37 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>หมอน ErgoLab Deep Sleep หมดปัญหาปวดคอ ไม่ต้องกังวลเรื่องกรน หลับสบายต่อเนื่องตลอดคืน (คืนเงินใน 90 วัน + รับประกัน 1 ปี)</v>
+        <v>ส่งจากไทย🚚ติดผนัง ที่เก็บแปรงแต่งหน้ากล่องใส่ของน่ารักชั้นวางของบนโต๊ะทํางานที่เก็บเครื่องเขียนบนเดส</v>
       </c>
       <c r="C4" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r98s-lop0pq60fv3x2c.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/cn-11134207-820l4-mo3ywk99wt1h85.webp</v>
       </c>
       <c r="D4" t="str">
-        <v>1411.00</v>
+        <v>138.00</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G4" t="str">
-        <v>ขายได้ 90พัน+ ชิ้น</v>
+        <v>ขายได้ 79 ชิ้น</v>
       </c>
       <c r="H4" t="str">
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>https://shopee.co.th/product/0/23922419352</v>
+        <v>https://shopee.co.th/product/0/54606642996</v>
       </c>
       <c r="J4" t="str">
-        <v>https://s.shopee.co.th/5fmAZ5DTpk</v>
+        <v>https://s.shopee.co.th/60PP7TFNUt</v>
       </c>
       <c r="K4" t="str">
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -556,37 +556,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Maybuck เครื่องตัดหญ้าเบนซิน GX-35 4 จังหวะสำหรับใช้ในครัวเรือน เครื่องตัดหญ้าไร้สายขนาดเล็กเครื่องตัดหญ้าน้ำมันเบนซิน</v>
+        <v>ส่งจากไทย🚚Miffy แก้วกาแฟ มัทฉะ ถ้วยมัทฉะ แก้วน้ำ แก้วการ์ตูน ตกแต่งคาเฟ่ ถ้วยเซรามิก ริเริ่มความคิด</v>
       </c>
       <c r="C5" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0t-mcg5v905zw3o82.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/cn-11134207-820l4-mk0m1nqpb6rl65.webp</v>
       </c>
       <c r="D5" t="str">
-        <v>2680.00</v>
+        <v>337.00</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G5" t="str">
-        <v>ขายได้ 3พัน+ ชิ้น</v>
+        <v>ขายได้ 134 ชิ้น</v>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>https://shopee.co.th/product/0/43259115829</v>
+        <v>https://shopee.co.th/product/0/44027481267</v>
       </c>
       <c r="J5" t="str">
-        <v>https://s.shopee.co.th/W44PaeA44</v>
+        <v>https://s.shopee.co.th/4Axkw6V9mV</v>
       </c>
       <c r="K5" t="str">
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -594,37 +594,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>CIVAGOxLucky Puppy （26oz/780ml） แก้วกาแฟสแตนเลสซับเซรามิกพร้อมฝาปิดกระติกน้ําสูญญากาศแก้วน้ําร้อนและเย็น</v>
+        <v>ถูกสุด (1 ขวดใหญ่) น้ำยาล้างจาน ซันไลต์ SunLight 3200ML ล้างจาน ซันไล ทำความสะอาด Sun Light สูตร เลม่อน เทอร์โบ</v>
       </c>
       <c r="C6" t="str">
-        <v>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-ml67nm0lt2q764.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/sg-11134201-7rccb-lrk78gtun9kb25.webp</v>
       </c>
       <c r="D6" t="str">
-        <v>470.00</v>
+        <v>199.00</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>53</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>ขายได้ 1พัน+ ชิ้น</v>
+        <v/>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>https://shopee.co.th/product/0/57956483494</v>
+        <v>https://shopee.co.th/product/0/25413114255</v>
       </c>
       <c r="J6" t="str">
-        <v>https://s.shopee.co.th/2qRzBsepmP</v>
+        <v>https://s.shopee.co.th/5fmYird7uy</v>
       </c>
       <c r="K6" t="str">
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -632,37 +632,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Mobi GARDEN เก้าอี้ปิกนิก พับได้ แบบพกพา สวยหรู สําหรับตั้งแคมป์กลางแจ้ง</v>
+        <v>DreaME 4 in 1 โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นสูง ด้วยกรอบรูปทรงคงที่ โซฟาปรับนอน สีเบจ Sofa</v>
       </c>
       <c r="C7" t="str">
-        <v>https://down-bs-th.img.susercontent.com/cn-11134207-7qukw-lh7ao27q1gpr5c.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztc-mldc4h2lai9sf9.webp</v>
       </c>
       <c r="D7" t="str">
-        <v>926.00</v>
+        <v>5199.00</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="G7" t="str">
-        <v>ขายได้ 4พัน+ ชิ้น</v>
+        <v>ขายได้ 173 ชิ้น</v>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>https://shopee.co.th/product/0/23069023714</v>
+        <v>https://shopee.co.th/product/0/50856679189</v>
       </c>
       <c r="J7" t="str">
-        <v>https://s.shopee.co.th/9Uyt88J1tR</v>
+        <v>https://s.shopee.co.th/5q5yvAgtMb</v>
       </c>
       <c r="K7" t="str">
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -670,31 +670,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ แบบพกพา พร้อมปั๊มลมในตัว ที่นอนลม แบบหนา 40/25ซม</v>
+        <v>เครื่องตัดหญ้า Makita RBC-411</v>
       </c>
       <c r="C8" t="str">
-        <v>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-m66kvsnez2tt31.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7rasa-m27pzsk6rzc4c3.webp</v>
       </c>
       <c r="D8" t="str">
-        <v>1039.00</v>
+        <v>1890.00</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>65</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>ขายได้ 10พัน+ ชิ้น</v>
+        <v>ขายได้ 205 ชิ้น</v>
       </c>
       <c r="H8" t="str">
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>https://shopee.co.th/product/0/25326987298</v>
+        <v>https://shopee.co.th/product/0/28852177674</v>
       </c>
       <c r="J8" t="str">
-        <v>https://s.shopee.co.th/6fehkvh5FI</v>
+        <v>https://s.shopee.co.th/9Kfr5bcZcA</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -708,37 +708,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>ลวดหนาม (ชุบกัลวาไนซ์) ยาว120-200m (เบอร์14 16 17) ล้อมรั้วราคาถูก ลวดหนามเหล็กติดรั้ว ล้อมรั้ว ลวดหนาม</v>
+        <v>TYESO รุ่นใหม่ 2026 แก้วเก็บความเย็นลายดอกไม้ 900ML แก้วเก็บอุณหภูมิสแตนเลส พร้อมหลอด เก็บเย็น 24H ร้อน 12H</v>
       </c>
       <c r="C9" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasc-m2hnsoh6jg0x67.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/cn-11134207-820l4-mpbmea7lcwel5d.webp</v>
       </c>
       <c r="D9" t="str">
-        <v>675.00</v>
+        <v>339.00</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G9" t="str">
-        <v>ขายได้ 3พัน+ ชิ้น</v>
+        <v>ขายได้ 590 ชิ้น</v>
       </c>
       <c r="H9" t="str">
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>https://shopee.co.th/product/0/5379453788</v>
+        <v>https://shopee.co.th/product/0/54857018813</v>
       </c>
       <c r="J9" t="str">
-        <v>https://s.shopee.co.th/1LdBP86PE9</v>
+        <v>https://s.shopee.co.th/W4SZNKAYm</v>
       </c>
       <c r="K9" t="str">
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>9</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="10">
@@ -746,37 +746,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>TYESO TS-8829 TS-8830 แก้วน้ําสุญญากาศ เก็บความเย็น และร้อน อเนกประสงค์ พร้อมหลอดดูด 1050 มล. 1200 มล.</v>
+        <v>เลื่อยยนต์ KingKong 5800 พร้อมโซ่และบาร์ 11.5" (ถูกต้องตามกฎหมาย)</v>
       </c>
       <c r="C10" t="str">
-        <v>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-m8n1ynp79ckycb.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/458f1fd228e6661f26f652666a79db64.webp</v>
       </c>
       <c r="D10" t="str">
-        <v>419.00</v>
+        <v>3200.00</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>46</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>ขายได้ 8พัน+ ชิ้น</v>
+        <v>ขายได้ 320 ชิ้น</v>
       </c>
       <c r="H10" t="str">
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>https://shopee.co.th/product/0/20385393992</v>
+        <v>https://shopee.co.th/product/0/4643745575</v>
       </c>
       <c r="J10" t="str">
-        <v>https://s.shopee.co.th/7AayLqsNaB</v>
+        <v>https://s.shopee.co.th/6VLfiP04sP</v>
       </c>
       <c r="K10" t="str">
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -784,31 +784,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>YAGE เครื่องดักยุง รุ่น โคมดักยุงระบบสัมผัส ดูดยุงร้ายให้ตายในทันที แบบ 360 องศา ปกป้องคนที่คุณรัก โคมดักยุง</v>
+        <v>Ozama บัลลังก์ รุ่น Alpha เก้าอี้เกมมิ่ง Gaming Chair by Tengu รับน้ำหนัก 150กก Throne of Gamer</v>
       </c>
       <c r="C11" t="str">
-        <v>https://down-bs-th.img.susercontent.com/9db66f2b508e0216fbd10afbdedebe8c.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztd-mpg3k7j4uq68f6.webp</v>
       </c>
       <c r="D11" t="str">
-        <v>497.00</v>
+        <v>6990.00</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G11" t="str">
-        <v>ขายได้ 60พัน+ ชิ้น</v>
+        <v>ขายได้ 3พัน+ ชิ้น</v>
       </c>
       <c r="H11" t="str">
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>https://shopee.co.th/product/0/4749406757</v>
+        <v>https://shopee.co.th/product/0/24014645473</v>
       </c>
       <c r="J11" t="str">
-        <v>https://s.shopee.co.th/5L9KAU8uki</v>
+        <v>https://s.shopee.co.th/5q5yvBBD0P</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -822,19 +822,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>TTRacing Duo V4 Chopper One Piece Edition Gaming Chair เก้าอี้สำนักงาน เก้าอี้เกมมิ่ง - รับประกัน 2 ปี</v>
+        <v>เครื่องตัดหญ้า 2 จังหวะ Robin 40.2ซีซี รุ่นNB411 2T สะพายข้าง ราคาถูก สตาร์ทติดง่าย ตัดหญ้า</v>
       </c>
       <c r="C12" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mp3thzgdxy4g51.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mg3m6m2ysqobec.webp</v>
       </c>
       <c r="D12" t="str">
-        <v>4821.00</v>
+        <v>3200.00</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>42</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v>ขายได้ 1พัน+ ชิ้น</v>
@@ -843,10 +843,10 @@
         <v/>
       </c>
       <c r="I12" t="str">
-        <v>https://shopee.co.th/product/0/24723053806</v>
+        <v>https://shopee.co.th/product/0/3740324474</v>
       </c>
       <c r="J12" t="str">
-        <v>https://s.shopee.co.th/6py7xFBexZ</v>
+        <v>https://s.shopee.co.th/2g8x9MVzkQ</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -860,37 +860,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>ก้านไม้หอมในบ้าน JASMALI GLASSHOUSE DIFFUSER ปริมาณ 180ML</v>
+        <v>แก้วเซรามิคแมวน่ารัก ด้ามจับเป็นแมว แก้วน้ำลายการ์ตูน แก้วกาแฟเซรามิก ของขวัญวันเกิดสุดคิวท์400ml</v>
       </c>
       <c r="C13" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zti-ml3hnx0lnuo587.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7rase-m9na6e5euezk7a.webp</v>
       </c>
       <c r="D13" t="str">
-        <v>204.00</v>
+        <v>138.00</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="G13" t="str">
-        <v>ขายได้ 20พัน+ ชิ้น</v>
+        <v>ขายได้ 522 ชิ้น</v>
       </c>
       <c r="H13" t="str">
         <v/>
       </c>
       <c r="I13" t="str">
-        <v>https://shopee.co.th/product/0/7348642178</v>
+        <v>https://shopee.co.th/product/0/40950538015</v>
       </c>
       <c r="J13" t="str">
-        <v>https://s.shopee.co.th/6VLHYdN6Re</v>
+        <v>https://s.shopee.co.th/7pr3IrQQ0Q</v>
       </c>
       <c r="K13" t="str">
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -898,37 +898,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>TYESO 01-01022/23/24/25/26 600ML/750MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญากาศพร้อมฝาปิด 2-in-1 และฟาง,ถ้วยกาแฟสแตนเลสผนังคู่แก้วเดินทางป้องกันการรั่วพลิก</v>
+        <v>Hygiene ไฮยีน สเปรย์หอมปรับผ้าเรียบเร็ว 220 มล. สเปรย์หอมเรียบ สเปรย์ปรับผ้าหอม ช่วยลดรอยยับ</v>
       </c>
       <c r="C14" t="str">
-        <v>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-mcd890h82m5o60.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7r98w-m002n9j8eqgxd8.webp</v>
       </c>
       <c r="D14" t="str">
-        <v>339.00</v>
+        <v>127.00</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G14" t="str">
-        <v>ขายได้ 20พัน+ ชิ้น</v>
+        <v>ขายได้ 4พัน+ ชิ้น</v>
       </c>
       <c r="H14" t="str">
         <v/>
       </c>
       <c r="I14" t="str">
-        <v>https://shopee.co.th/product/0/43304958355</v>
+        <v>https://shopee.co.th/product/0/25635880688</v>
       </c>
       <c r="J14" t="str">
-        <v>https://s.shopee.co.th/1BJlCpoQ0x</v>
+        <v>https://s.shopee.co.th/9AMQtJPT2E</v>
       </c>
       <c r="K14" t="str">
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -936,37 +936,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>Sipeau 5เเพ็ค กระดาษทิชชู่แบบแขวน หนาเป็นพิเศษ ทนน้ำ ใช้ได้ทั้งแบบดึงด้านล่างและแบบดึงด้านบน เหมาะสำหรับใช้ในบ้าน</v>
+        <v>เก้าอี้โยก , เก้าอี้พักผ่อน ,เก้าอี้นุ่ม ,เก้าอี้โยกหุ้มนุ่ม ,เก้าอี้โซฟา ,เก้าอี้โยก ,เก้าอี้โซฟาเดี่ยว</v>
       </c>
       <c r="C15" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm8sx4c89iwz52.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/cn-11134207-820l4-mld5o6ty6juo43.webp</v>
       </c>
       <c r="D15" t="str">
-        <v>89.00</v>
+        <v>359.00</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G15" t="str">
-        <v>ขายได้ 6พัน+ ชิ้น</v>
+        <v>ขายได้ 56 ชิ้น</v>
       </c>
       <c r="H15" t="str">
         <v/>
       </c>
       <c r="I15" t="str">
-        <v>https://shopee.co.th/product/0/45957704286</v>
+        <v>https://shopee.co.th/product/0/46556705417</v>
       </c>
       <c r="J15" t="str">
-        <v>https://s.shopee.co.th/8ATVXhS24W</v>
+        <v>https://s.shopee.co.th/5fmYisqstO</v>
       </c>
       <c r="K15" t="str">
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -974,13 +974,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้าเดียว(คิตตี้,คุโรมิ,ชินนาม่อนโรล,มายเมโลดี้)ประกัน 1ปี</v>
+        <v>โคมไฟตั้งพื้น LED สไตล์โมเดิร์น สามารถปรับความสว่างได้ ตกแต่งห้องนั่งเล่น</v>
       </c>
       <c r="C16" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mozceyjaky69f5.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/sg-11134201-8224r-mhol31jcaholea.webp</v>
       </c>
       <c r="D16" t="str">
-        <v>3851.00</v>
+        <v>569.00</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -989,22 +989,22 @@
         <v>29</v>
       </c>
       <c r="G16" t="str">
-        <v>ขายได้ 4พัน+ ชิ้น</v>
+        <v>ขายได้ 3พัน+ ชิ้น</v>
       </c>
       <c r="H16" t="str">
         <v/>
       </c>
       <c r="I16" t="str">
-        <v>https://shopee.co.th/product/0/16761796915</v>
+        <v>https://shopee.co.th/product/0/54802352443</v>
       </c>
       <c r="J16" t="str">
-        <v>https://s.shopee.co.th/4VaDAxu5GU</v>
+        <v>https://s.shopee.co.th/60PP7UxWN7</v>
       </c>
       <c r="K16" t="str">
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1012,37 +1012,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ไม่ต้องเจาะ ที่วางของในห้องน้ำ ชั้นใส่ของ</v>
+        <v>คอนโดเก็บอาหาร กล่องใส่อาหาร ฝาครอบอาหาร 3/4/5 ชั้นเก็บอุณหภูมิ ชั้นวางอาหาร Stacy Food Cover</v>
       </c>
       <c r="C17" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mkjqydbkcq9x48.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7r98p-lq9499no64tg95.webp</v>
       </c>
       <c r="D17" t="str">
-        <v>169.00</v>
+        <v>80.00</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>49</v>
       </c>
       <c r="G17" t="str">
-        <v>ขายได้ 151 ชิ้น</v>
+        <v>ขายได้ 4พัน+ ชิ้น</v>
       </c>
       <c r="H17" t="str">
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>https://shopee.co.th/product/0/51106057326</v>
+        <v>https://shopee.co.th/product/0/18780727001</v>
       </c>
       <c r="J17" t="str">
-        <v>https://s.shopee.co.th/80A5LOksuD</v>
+        <v>https://s.shopee.co.th/4LHB8R99ws</v>
       </c>
       <c r="K17" t="str">
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
@@ -1050,19 +1050,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>TYESO TS-8826 TS-8827 TS-8828 600 มล. 750 มล. 900 มล. แก้วน้ําสูญญากาศ เก็บความเย็น และร้อน อเนกประสงค์ พร้อมหลอดดูด</v>
+        <v>มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ ถูบ้าน ปลอดภัยกับเด็ก และ สัตว์เลี้ยง มิลินคลีน</v>
       </c>
       <c r="C18" t="str">
-        <v>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mel4uxcc4hz7fd.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7r98o-lzhrgu8c0n8pfe.webp</v>
       </c>
       <c r="D18" t="str">
-        <v>329.00</v>
+        <v>296.00</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G18" t="str">
         <v>ขายได้ 10พัน+ ชิ้น</v>
@@ -1071,16 +1071,16 @@
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>https://shopee.co.th/product/0/20285394571</v>
+        <v>https://shopee.co.th/product/0/29805541583</v>
       </c>
       <c r="J18" t="str">
-        <v>https://s.shopee.co.th/1gG1nlJ22I</v>
+        <v>https://s.shopee.co.th/AKYOHStbZL</v>
       </c>
       <c r="K18" t="str">
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -1088,37 +1088,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>มิลิน น้ำยาทำความสะอาดอเนกประสงค์ ขัดห้องน้ำ ถูบ้าน ปลอดภัยกับเด็ก และ สัตว์เลี้ยง มิลินคลีน</v>
+        <v>ตู้รองเท้าเหล็ก ตู้รองเท้า บางเฉียบ 12.2ซม แข็งแรง กันน้ำและกันสนิม ใช้ได้ทั้งในบ้านและนอกบ้าน ประกัน1ปี</v>
       </c>
       <c r="C19" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r98o-lzhrgu8c0n8pfe.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7ras9-m66pbx8t6s2l68.webp</v>
       </c>
       <c r="D19" t="str">
-        <v>294.00</v>
+        <v>316.00</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="G19" t="str">
-        <v>ขายได้ 10พัน+ ชิ้น</v>
+        <v>ขายได้ 318 ชิ้น</v>
       </c>
       <c r="H19" t="str">
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>https://shopee.co.th/product/0/29805541583</v>
+        <v>https://shopee.co.th/product/0/26376049757</v>
       </c>
       <c r="J19" t="str">
-        <v>https://s.shopee.co.th/3LOFmpJlfB</v>
+        <v>https://s.shopee.co.th/3qKuXWRuCs</v>
       </c>
       <c r="K19" t="str">
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -1126,37 +1126,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ถึง160°c สีครีม เบาะฟองน้ำหนา10ซม. นุ่มสบาย ผ้ากำมะหยี่</v>
+        <v>พร้อมส่ง 🚚 ใหม่น่ารัก มิฟฟี่ กระต่ายตุ๊กตาตุ๊กตาหมอนสําหรับแฟนของขวัญวันเกิดเตียงเบาะนอนของขวัญปีใหม่</v>
       </c>
       <c r="C20" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasb-m2j22x5ii5d008.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/sg-11134201-81zv9-miz9ow3oi8lj42.webp</v>
       </c>
       <c r="D20" t="str">
-        <v>1499.00</v>
+        <v>77.00</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="G20" t="str">
-        <v>ขายได้ 43 ชิ้น</v>
+        <v>ขายได้ 42 ชิ้น</v>
       </c>
       <c r="H20" t="str">
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>https://shopee.co.th/product/0/27467423728</v>
+        <v>https://shopee.co.th/product/0/54504026723</v>
       </c>
       <c r="J20" t="str">
-        <v>https://s.shopee.co.th/9pbjWm5Xax</v>
+        <v>https://s.shopee.co.th/1qZq9qj4iN</v>
       </c>
       <c r="K20" t="str">
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1164,37 +1164,37 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>ก้านไม้หอมในสปา JASMALI GLASSHOUSE DIFFUSER ปริมาณ 180ML</v>
+        <v>CIVAGO（40oz/1200ml）แก้วสแตนเลสเกรดอาหารแบบเก็บความเย็น มีหูหิ้วและหลอด ความจุใหญ่ สำหรับกาแฟเย็น ขวดน้ำ แก้วน้ำแฟชั่น ของขวัญผู้หญิง</v>
       </c>
       <c r="C21" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zte-ml3hoam25nggae.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/cn-11134207-820l4-mnzjnlxk7dhec1.webp</v>
       </c>
       <c r="D21" t="str">
-        <v>223.00</v>
+        <v>629.00</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="G21" t="str">
-        <v>ขายได้ 7พัน+ ชิ้น</v>
+        <v>ขายได้ 156 ชิ้น</v>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>https://shopee.co.th/product/0/28223885891</v>
+        <v>https://shopee.co.th/product/0/27794790818</v>
       </c>
       <c r="J21" t="str">
-        <v>https://s.shopee.co.th/9pbjWmDzqV</v>
+        <v>https://s.shopee.co.th/2VpWx4oRWx</v>
       </c>
       <c r="K21" t="str">
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
